--- a/artistresponses.xlsx
+++ b/artistresponses.xlsx
@@ -44,7 +44,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,16 @@
         <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0001FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0038761D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -105,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -155,6 +165,8 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -44104,7 +44116,7 @@
       <c r="A202" s="15" t="n">
         <v>46196.57164936342</v>
       </c>
-      <c r="B202" s="17" t="inlineStr">
+      <c r="B202" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44157,7 +44169,7 @@
       <c r="A203" s="15" t="n">
         <v>46196.58040884259</v>
       </c>
-      <c r="B203" s="17" t="inlineStr">
+      <c r="B203" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44210,7 +44222,7 @@
       <c r="A204" s="15" t="n">
         <v>46196.58475002315</v>
       </c>
-      <c r="B204" s="17" t="inlineStr">
+      <c r="B204" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44268,7 +44280,7 @@
       <c r="A205" s="15" t="n">
         <v>46196.60498108796</v>
       </c>
-      <c r="B205" s="17" t="inlineStr">
+      <c r="B205" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44316,7 +44328,7 @@
       <c r="A206" s="15" t="n">
         <v>46196.60913241898</v>
       </c>
-      <c r="B206" s="17" t="inlineStr">
+      <c r="B206" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44374,7 +44386,7 @@
       <c r="A207" s="15" t="n">
         <v>46196.61649114583</v>
       </c>
-      <c r="B207" s="17" t="inlineStr">
+      <c r="B207" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44427,7 +44439,7 @@
       <c r="A208" s="15" t="n">
         <v>46196.62613255787</v>
       </c>
-      <c r="B208" s="17" t="inlineStr">
+      <c r="B208" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44484,7 +44496,7 @@
       <c r="A209" s="15" t="n">
         <v>46196.63270076389</v>
       </c>
-      <c r="B209" s="17" t="inlineStr">
+      <c r="B209" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44543,7 +44555,7 @@
       <c r="A210" s="15" t="n">
         <v>46196.64567524305</v>
       </c>
-      <c r="B210" s="17" t="inlineStr">
+      <c r="B210" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44596,7 +44608,7 @@
       <c r="A211" s="15" t="n">
         <v>46196.67400303241</v>
       </c>
-      <c r="B211" s="17" t="inlineStr">
+      <c r="B211" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44654,7 +44666,7 @@
       <c r="A212" s="15" t="n">
         <v>46196.6756765625</v>
       </c>
-      <c r="B212" s="17" t="inlineStr">
+      <c r="B212" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44702,7 +44714,7 @@
       <c r="A213" s="15" t="n">
         <v>46196.67757846065</v>
       </c>
-      <c r="B213" s="17" t="inlineStr">
+      <c r="B213" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44760,7 +44772,7 @@
       <c r="A214" s="15" t="n">
         <v>46196.68747168982</v>
       </c>
-      <c r="B214" s="17" t="inlineStr">
+      <c r="B214" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44813,7 +44825,7 @@
       <c r="A215" s="15" t="n">
         <v>46196.71159765046</v>
       </c>
-      <c r="B215" s="17" t="inlineStr">
+      <c r="B215" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44861,7 +44873,7 @@
       <c r="A216" s="15" t="n">
         <v>46196.71306248842</v>
       </c>
-      <c r="B216" s="17" t="inlineStr">
+      <c r="B216" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44920,7 +44932,7 @@
       <c r="A217" s="15" t="n">
         <v>46196.71517428241</v>
       </c>
-      <c r="B217" s="17" t="inlineStr">
+      <c r="B217" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -44974,7 +44986,7 @@
       <c r="A218" s="15" t="n">
         <v>46196.7270652662</v>
       </c>
-      <c r="B218" s="17" t="inlineStr">
+      <c r="B218" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45032,7 +45044,7 @@
       <c r="A219" s="15" t="n">
         <v>46196.75845607639</v>
       </c>
-      <c r="B219" s="17" t="inlineStr">
+      <c r="B219" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45092,7 +45104,7 @@
       <c r="A220" s="15" t="n">
         <v>46196.76162001157</v>
       </c>
-      <c r="B220" s="17" t="inlineStr">
+      <c r="B220" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45150,7 +45162,7 @@
       <c r="A221" s="15" t="n">
         <v>46196.7654258449</v>
       </c>
-      <c r="B221" s="17" t="inlineStr">
+      <c r="B221" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45208,7 +45220,7 @@
       <c r="A222" s="15" t="n">
         <v>46196.77222366898</v>
       </c>
-      <c r="B222" s="17" t="inlineStr">
+      <c r="B222" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45266,7 +45278,7 @@
       <c r="A223" s="15" t="n">
         <v>46196.77429320602</v>
       </c>
-      <c r="B223" s="17" t="inlineStr">
+      <c r="B223" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45327,7 +45339,7 @@
       <c r="A224" s="15" t="n">
         <v>46196.78033703704</v>
       </c>
-      <c r="B224" s="17" t="inlineStr">
+      <c r="B224" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45388,7 +45400,7 @@
       <c r="A225" s="15" t="n">
         <v>46196.78680172453</v>
       </c>
-      <c r="B225" s="17" t="inlineStr">
+      <c r="B225" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45441,7 +45453,7 @@
       <c r="A226" s="15" t="n">
         <v>46196.79345650463</v>
       </c>
-      <c r="B226" s="17" t="inlineStr">
+      <c r="B226" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45495,7 +45507,7 @@
       <c r="A227" s="15" t="n">
         <v>46196.8135378588</v>
       </c>
-      <c r="B227" s="17" t="inlineStr">
+      <c r="B227" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45553,7 +45565,7 @@
       <c r="A228" s="15" t="n">
         <v>46196.83133381944</v>
       </c>
-      <c r="B228" s="17" t="inlineStr">
+      <c r="B228" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45606,7 +45618,7 @@
       <c r="A229" s="15" t="n">
         <v>46196.83394200231</v>
       </c>
-      <c r="B229" s="17" t="inlineStr">
+      <c r="B229" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45664,7 +45676,7 @@
       <c r="A230" s="15" t="n">
         <v>46196.84065604167</v>
       </c>
-      <c r="B230" s="17" t="inlineStr">
+      <c r="B230" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45722,7 +45734,7 @@
       <c r="A231" s="15" t="n">
         <v>46196.87363641203</v>
       </c>
-      <c r="B231" s="17" t="inlineStr">
+      <c r="B231" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45780,7 +45792,7 @@
       <c r="A232" s="15" t="n">
         <v>46196.87951961806</v>
       </c>
-      <c r="B232" s="17" t="inlineStr">
+      <c r="B232" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45833,7 +45845,7 @@
       <c r="A233" s="15" t="n">
         <v>46196.89181947917</v>
       </c>
-      <c r="B233" s="17" t="inlineStr">
+      <c r="B233" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45891,7 +45903,7 @@
       <c r="A234" s="15" t="n">
         <v>46196.89535434027</v>
       </c>
-      <c r="B234" s="17" t="inlineStr">
+      <c r="B234" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45951,7 +45963,7 @@
       <c r="A235" s="15" t="n">
         <v>46196.89930099537</v>
       </c>
-      <c r="B235" s="17" t="inlineStr">
+      <c r="B235" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -45999,7 +46011,7 @@
       <c r="A236" s="15" t="n">
         <v>46196.91160763889</v>
       </c>
-      <c r="B236" s="17" t="inlineStr">
+      <c r="B236" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46057,7 +46069,7 @@
       <c r="A237" s="15" t="n">
         <v>46196.95104177083</v>
       </c>
-      <c r="B237" s="17" t="inlineStr">
+      <c r="B237" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46115,7 +46127,7 @@
       <c r="A238" s="15" t="n">
         <v>46196.95276800926</v>
       </c>
-      <c r="B238" s="17" t="inlineStr">
+      <c r="B238" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46173,7 +46185,7 @@
       <c r="A239" s="15" t="n">
         <v>46196.96063599537</v>
       </c>
-      <c r="B239" s="17" t="inlineStr">
+      <c r="B239" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46231,7 +46243,7 @@
       <c r="A240" s="15" t="n">
         <v>46196.97801758102</v>
       </c>
-      <c r="B240" s="17" t="inlineStr">
+      <c r="B240" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/artistresponses.xlsx
+++ b/artistresponses.xlsx
@@ -46291,7 +46291,7 @@
       <c r="A241" s="15" t="n">
         <v>46197.06481839121</v>
       </c>
-      <c r="B241" s="17" t="inlineStr">
+      <c r="B241" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46349,7 +46349,7 @@
       <c r="A242" s="15" t="n">
         <v>46197.06512855324</v>
       </c>
-      <c r="B242" s="17" t="inlineStr">
+      <c r="B242" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46407,7 +46407,7 @@
       <c r="A243" s="15" t="n">
         <v>46197.07306454861</v>
       </c>
-      <c r="B243" s="17" t="inlineStr">
+      <c r="B243" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46465,7 +46465,7 @@
       <c r="A244" s="15" t="n">
         <v>46197.07413665509</v>
       </c>
-      <c r="B244" s="17" t="inlineStr">
+      <c r="B244" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46518,7 +46518,7 @@
       <c r="A245" s="15" t="n">
         <v>46197.09886752315</v>
       </c>
-      <c r="B245" s="17" t="inlineStr">
+      <c r="B245" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46571,7 +46571,7 @@
       <c r="A246" s="15" t="n">
         <v>46197.10280880787</v>
       </c>
-      <c r="B246" s="17" t="inlineStr">
+      <c r="B246" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46629,7 +46629,7 @@
       <c r="A247" s="15" t="n">
         <v>46197.10454234954</v>
       </c>
-      <c r="B247" s="17" t="inlineStr">
+      <c r="B247" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46682,7 +46682,7 @@
       <c r="A248" s="15" t="n">
         <v>46197.111048125</v>
       </c>
-      <c r="B248" s="17" t="inlineStr">
+      <c r="B248" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/artistresponses.xlsx
+++ b/artistresponses.xlsx
@@ -46730,7 +46730,7 @@
       <c r="A249" s="15" t="n">
         <v>46197.1168015162</v>
       </c>
-      <c r="B249" s="17" t="inlineStr">
+      <c r="B249" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46783,7 +46783,7 @@
       <c r="A250" s="15" t="n">
         <v>46197.11879928241</v>
       </c>
-      <c r="B250" s="17" t="inlineStr">
+      <c r="B250" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46841,7 +46841,7 @@
       <c r="A251" s="15" t="n">
         <v>46197.12177651621</v>
       </c>
-      <c r="B251" s="17" t="inlineStr">
+      <c r="B251" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46889,7 +46889,7 @@
       <c r="A252" s="15" t="n">
         <v>46197.12565512732</v>
       </c>
-      <c r="B252" s="17" t="inlineStr">
+      <c r="B252" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46947,7 +46947,7 @@
       <c r="A253" s="15" t="n">
         <v>46197.13672293982</v>
       </c>
-      <c r="B253" s="17" t="inlineStr">
+      <c r="B253" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -46995,7 +46995,7 @@
       <c r="A254" s="15" t="n">
         <v>46197.14916981482</v>
       </c>
-      <c r="B254" s="17" t="inlineStr">
+      <c r="B254" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47048,7 +47048,7 @@
       <c r="A255" s="15" t="n">
         <v>46197.16875571759</v>
       </c>
-      <c r="B255" s="17" t="inlineStr">
+      <c r="B255" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47106,7 +47106,7 @@
       <c r="A256" s="15" t="n">
         <v>46197.17491487269</v>
       </c>
-      <c r="B256" s="17" t="inlineStr">
+      <c r="B256" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47161,7 +47161,7 @@
       <c r="A257" s="15" t="n">
         <v>46197.18000943287</v>
       </c>
-      <c r="B257" s="17" t="inlineStr">
+      <c r="B257" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47220,7 +47220,7 @@
       <c r="A258" s="15" t="n">
         <v>46197.182648125</v>
       </c>
-      <c r="B258" s="17" t="inlineStr">
+      <c r="B258" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47273,7 +47273,7 @@
       <c r="A259" s="15" t="n">
         <v>46197.19624737268</v>
       </c>
-      <c r="B259" s="17" t="inlineStr">
+      <c r="B259" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47321,7 +47321,7 @@
       <c r="A260" s="15" t="n">
         <v>46197.21134708334</v>
       </c>
-      <c r="B260" s="17" t="inlineStr">
+      <c r="B260" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47374,7 +47374,7 @@
       <c r="A261" s="15" t="n">
         <v>46197.22971452546</v>
       </c>
-      <c r="B261" s="17" t="inlineStr">
+      <c r="B261" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47432,7 +47432,7 @@
       <c r="A262" s="15" t="n">
         <v>46197.23280884259</v>
       </c>
-      <c r="B262" s="17" t="inlineStr">
+      <c r="B262" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47480,7 +47480,7 @@
       <c r="A263" s="15" t="n">
         <v>46197.25549875</v>
       </c>
-      <c r="B263" s="17" t="inlineStr">
+      <c r="B263" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47538,7 +47538,7 @@
       <c r="A264" s="15" t="n">
         <v>46197.28423890047</v>
       </c>
-      <c r="B264" s="17" t="inlineStr">
+      <c r="B264" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47596,7 +47596,7 @@
       <c r="A265" s="15" t="n">
         <v>46197.29312059028</v>
       </c>
-      <c r="B265" s="17" t="inlineStr">
+      <c r="B265" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47654,7 +47654,7 @@
       <c r="A266" s="15" t="n">
         <v>46197.31243127315</v>
       </c>
-      <c r="B266" s="17" t="inlineStr">
+      <c r="B266" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47712,7 +47712,7 @@
       <c r="A267" s="15" t="n">
         <v>46197.31774209491</v>
       </c>
-      <c r="B267" s="17" t="inlineStr">
+      <c r="B267" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47770,7 +47770,7 @@
       <c r="A268" s="15" t="n">
         <v>46197.32154927083</v>
       </c>
-      <c r="B268" s="17" t="inlineStr">
+      <c r="B268" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47828,7 +47828,7 @@
       <c r="A269" s="15" t="n">
         <v>46197.33270748843</v>
       </c>
-      <c r="B269" s="17" t="inlineStr">
+      <c r="B269" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47881,7 +47881,7 @@
       <c r="A270" s="15" t="n">
         <v>46197.33577320602</v>
       </c>
-      <c r="B270" s="17" t="inlineStr">
+      <c r="B270" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47934,7 +47934,7 @@
       <c r="A271" s="15" t="n">
         <v>46197.34254753472</v>
       </c>
-      <c r="B271" s="17" t="inlineStr">
+      <c r="B271" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -47992,7 +47992,7 @@
       <c r="A272" s="15" t="n">
         <v>46197.34652880787</v>
       </c>
-      <c r="B272" s="17" t="inlineStr">
+      <c r="B272" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48045,7 +48045,7 @@
       <c r="A273" s="15" t="n">
         <v>46197.34828741898</v>
       </c>
-      <c r="B273" s="17" t="inlineStr">
+      <c r="B273" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48098,7 +48098,7 @@
       <c r="A274" s="15" t="n">
         <v>46197.37070707176</v>
       </c>
-      <c r="B274" s="17" t="inlineStr">
+      <c r="B274" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48146,7 +48146,7 @@
       <c r="A275" s="15" t="n">
         <v>46197.41466622685</v>
       </c>
-      <c r="B275" s="17" t="inlineStr">
+      <c r="B275" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48204,7 +48204,7 @@
       <c r="A276" s="15" t="n">
         <v>46197.41812456019</v>
       </c>
-      <c r="B276" s="17" t="inlineStr">
+      <c r="B276" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48257,7 +48257,7 @@
       <c r="A277" s="15" t="n">
         <v>46197.46035231482</v>
       </c>
-      <c r="B277" s="17" t="inlineStr">
+      <c r="B277" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48318,7 +48318,7 @@
       <c r="A278" s="15" t="n">
         <v>46197.46123776621</v>
       </c>
-      <c r="B278" s="17" t="inlineStr">
+      <c r="B278" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48366,7 +48366,7 @@
       <c r="A279" s="15" t="n">
         <v>46197.46717019676</v>
       </c>
-      <c r="B279" s="17" t="inlineStr">
+      <c r="B279" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48424,7 +48424,7 @@
       <c r="A280" s="15" t="n">
         <v>46197.47157598379</v>
       </c>
-      <c r="B280" s="17" t="inlineStr">
+      <c r="B280" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48477,7 +48477,7 @@
       <c r="A281" s="15" t="n">
         <v>46197.50344618056</v>
       </c>
-      <c r="B281" s="17" t="inlineStr">
+      <c r="B281" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48530,7 +48530,7 @@
       <c r="A282" s="15" t="n">
         <v>46197.50682341435</v>
       </c>
-      <c r="B282" s="17" t="inlineStr">
+      <c r="B282" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48588,7 +48588,7 @@
       <c r="A283" s="15" t="n">
         <v>46197.51753903935</v>
       </c>
-      <c r="B283" s="17" t="inlineStr">
+      <c r="B283" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48641,7 +48641,7 @@
       <c r="A284" s="15" t="n">
         <v>46197.53682021991</v>
       </c>
-      <c r="B284" s="17" t="inlineStr">
+      <c r="B284" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48699,7 +48699,7 @@
       <c r="A285" s="15" t="n">
         <v>46197.540485625</v>
       </c>
-      <c r="B285" s="17" t="inlineStr">
+      <c r="B285" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48752,7 +48752,7 @@
       <c r="A286" s="15" t="n">
         <v>46197.54334363426</v>
       </c>
-      <c r="B286" s="17" t="inlineStr">
+      <c r="B286" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48805,7 +48805,7 @@
       <c r="A287" s="15" t="n">
         <v>46197.55508130787</v>
       </c>
-      <c r="B287" s="17" t="inlineStr">
+      <c r="B287" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48848,7 +48848,7 @@
       <c r="A288" s="15" t="n">
         <v>46197.5638043287</v>
       </c>
-      <c r="B288" s="17" t="inlineStr">
+      <c r="B288" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48901,7 +48901,7 @@
       <c r="A289" s="15" t="n">
         <v>46197.57311896991</v>
       </c>
-      <c r="B289" s="17" t="inlineStr">
+      <c r="B289" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -48959,7 +48959,7 @@
       <c r="A290" s="15" t="n">
         <v>46197.59243184028</v>
       </c>
-      <c r="B290" s="17" t="inlineStr">
+      <c r="B290" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49017,7 +49017,7 @@
       <c r="A291" s="15" t="n">
         <v>46197.60245804398</v>
       </c>
-      <c r="B291" s="17" t="inlineStr">
+      <c r="B291" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49070,7 +49070,7 @@
       <c r="A292" s="15" t="n">
         <v>46197.63475246528</v>
       </c>
-      <c r="B292" s="17" t="inlineStr">
+      <c r="B292" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49123,7 +49123,7 @@
       <c r="A293" s="15" t="n">
         <v>46197.6349550926</v>
       </c>
-      <c r="B293" s="17" t="inlineStr">
+      <c r="B293" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49161,7 +49161,7 @@
       <c r="A294" s="15" t="n">
         <v>46197.65915452546</v>
       </c>
-      <c r="B294" s="17" t="inlineStr">
+      <c r="B294" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49214,7 +49214,7 @@
       <c r="A295" s="15" t="n">
         <v>46197.66569631945</v>
       </c>
-      <c r="B295" s="17" t="inlineStr">
+      <c r="B295" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49267,7 +49267,7 @@
       <c r="A296" s="15" t="n">
         <v>46197.6679309375</v>
       </c>
-      <c r="B296" s="17" t="inlineStr">
+      <c r="B296" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49320,7 +49320,7 @@
       <c r="A297" s="15" t="n">
         <v>46197.6800255787</v>
       </c>
-      <c r="B297" s="17" t="inlineStr">
+      <c r="B297" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49378,7 +49378,7 @@
       <c r="A298" s="15" t="n">
         <v>46197.69393487269</v>
       </c>
-      <c r="B298" s="17" t="inlineStr">
+      <c r="B298" s="26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49431,7 +49431,7 @@
       <c r="A299" s="15" t="n">
         <v>46197.71561207176</v>
       </c>
-      <c r="B299" s="17" t="inlineStr">
+      <c r="B299" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -49484,7 +49484,7 @@
       <c r="A300" s="15" t="n">
         <v>46197.71989388889</v>
       </c>
-      <c r="B300" s="17" t="inlineStr">
+      <c r="B300" s="25" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
